--- a/research/BFG.NZ/Reports/BFG.NZ_DCF_Model.xlsx
+++ b/research/BFG.NZ/Reports/BFG.NZ_DCF_Model.xlsx
@@ -1966,9 +1966,10 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="8">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B10" s="5">
         <f>SUM(B6:B8)</f>
